--- a/experiment_results/combined_sweep/rtt_bursts_S3_atk10pct_wu500000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S3_atk10pct_wu500000.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:009.7</t>
+          <t>00:010.0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22.4</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,12 +516,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -533,27 +533,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:020.3</t>
+          <t>00:018.9</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>241.3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>76.82</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>31795</t>
+          <t>320357</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -590,27 +590,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:030.2</t>
+          <t>00:031.5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>187.6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>290.9</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>7.86</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>120064</t>
+          <t>777108</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -647,27 +647,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:040.1</t>
+          <t>00:038.7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>120.2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>101.3</t>
+          <t>265.6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6.36</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>195977</t>
+          <t>1039749</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -704,27 +704,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:049.9</t>
+          <t>00:050.2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>60.6</t>
+          <t>115.8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>234.4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>238183</t>
+          <t>1242014</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -761,27 +761,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01:000.2</t>
+          <t>00:059.5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>58.7</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>276034</t>
+          <t>1375726</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -818,27 +818,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:010.0</t>
+          <t>01:010.7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>112.6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>231.2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>12.42</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>313918</t>
+          <t>1553986</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -880,22 +880,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>158.8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>330.1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>8.27</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>351829</t>
+          <t>1858842</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -932,27 +932,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:030.1</t>
+          <t>01:030.3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>198.1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>102.7</t>
+          <t>369.1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>410307</t>
+          <t>2213409</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -989,27 +989,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:040.1</t>
+          <t>01:040.5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>184.1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>353.0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>470411</t>
+          <t>2541453</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1046,27 +1046,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:050.0</t>
+          <t>01:049.8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>154.2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>63.8</t>
+          <t>296.1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,17 +1076,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>503853</t>
+          <t>2799852</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1103,27 +1103,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01:060.0</t>
+          <t>02:001.0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>121.4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>201.8</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5.84</t>
+          <t>4.62</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>536916</t>
+          <t>2999155</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1160,27 +1160,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:010.1</t>
+          <t>02:010.7</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>161.1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>566423</t>
+          <t>3155651</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:020.0</t>
+          <t>02:019.7</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>62.1</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>207.9</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>612123</t>
+          <t>3326480</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:030.0</t>
+          <t>02:030.5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>62.9</t>
+          <t>151.7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>305.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>9.28</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>659906</t>
+          <t>3572174</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1331,27 +1331,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:039.6</t>
+          <t>02:041.2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>105.2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>242.3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>667704</t>
+          <t>3733873</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1381,34 +1381,34 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:049.8</t>
+          <t>02:050.1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>99.9</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>6.62</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>652495</t>
+          <t>3763000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1445,27 +1445,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02:055.0</t>
+          <t>02:055.7</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1475,17 +1475,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>644941</t>
+          <t>3764705</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1494,6 +1494,63 @@
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>Normal/Residual</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>03:000.9</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>53.3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>53.6</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>7.32</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3766264</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>Normal/Residual</t>
         </is>

--- a/experiment_results/combined_sweep/rtt_bursts_S3_atk10pct_wu500000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S3_atk10pct_wu500000.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,17 +481,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -533,27 +533,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:018.9</t>
+          <t>00:019.2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>241.3</t>
+          <t>190.9</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>76.82</t>
+          <t>65.58</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>320357</t>
+          <t>290875</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -590,27 +590,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:031.5</t>
+          <t>00:029.5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>187.6</t>
+          <t>236.7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>290.9</t>
+          <t>291.5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>7.86</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>777108</t>
+          <t>697053</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -647,27 +647,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:038.7</t>
+          <t>00:041.1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>120.2</t>
+          <t>100.7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>265.6</t>
+          <t>230.9</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1039749</t>
+          <t>824947</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -704,27 +704,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:050.2</t>
+          <t>00:049.6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>115.8</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>234.4</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1242014</t>
+          <t>880230</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -761,27 +761,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00:059.5</t>
+          <t>00:059.4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>191.9</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>16.72</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1375726</t>
+          <t>998396</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -818,27 +818,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01:010.7</t>
+          <t>01:010.4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>112.6</t>
+          <t>114.8</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>231.2</t>
+          <t>205.9</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>12.42</t>
+          <t>8.55</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1553986</t>
+          <t>1114172</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -875,27 +875,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:019.7</t>
+          <t>01:020.3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>158.8</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>330.1</t>
+          <t>154.7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>4.37</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1858842</t>
+          <t>1213386</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -932,27 +932,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:030.3</t>
+          <t>01:030.1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>198.1</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>369.1</t>
+          <t>257.3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2213409</t>
+          <t>1376422</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -989,17 +989,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:040.5</t>
+          <t>01:039.9</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>184.1</t>
+          <t>156.4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>353.0</t>
+          <t>276.4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2541453</t>
+          <t>1553283</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1046,27 +1046,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:049.8</t>
+          <t>01:050.5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>154.2</t>
+          <t>157.9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>296.1</t>
+          <t>264.5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2799852</t>
+          <t>1735906</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1103,27 +1103,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02:001.0</t>
+          <t>02:000.3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>121.4</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>201.8</t>
+          <t>261.3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2999155</t>
+          <t>1930980</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1160,27 +1160,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:010.7</t>
+          <t>02:009.4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>159.4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>161.1</t>
+          <t>259.2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3155651</t>
+          <t>2119191</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1217,27 +1217,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02:019.7</t>
+          <t>02:020.0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>150.3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>207.9</t>
+          <t>244.3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3326480</t>
+          <t>2275152</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:030.5</t>
+          <t>02:029.8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>151.7</t>
+          <t>191.2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>305.0</t>
+          <t>314.6</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3572174</t>
+          <t>2492716</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1331,27 +1331,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02:041.2</t>
+          <t>02:040.3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>105.2</t>
+          <t>161.3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>242.3</t>
+          <t>322.2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3733873</t>
+          <t>2675361</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1388,27 +1388,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:050.1</t>
+          <t>02:050.0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>99.9</t>
+          <t>125.3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>6.62</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3763000</t>
+          <t>2688278</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1445,47 +1445,47 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02:055.7</t>
+          <t>02:054.9</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>38.6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3764705</t>
+          <t>2683185</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1494,63 +1494,6 @@
         </is>
       </c>
       <c r="K19" t="inlineStr">
-        <is>
-          <t>Normal/Residual</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>03:000.9</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>53.3</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>53.6</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0.43</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>7.32</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>3766264</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
         <is>
           <t>Normal/Residual</t>
         </is>
